--- a/测试环境/小表3.xlsx
+++ b/测试环境/小表3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c4e8455bcdffc71/Desktop/发送到服务器的文件/excel小表并大表/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c4e8455bcdffc71/Desktop/excel小表并大表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_AD4DA82427541F7ACA7EB8D5404B1EBE6AE8DE11" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D951182A-1B5A-4D60-AB85-FA5F952DE15A}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_AD4DA82427541F7ACA7EB8D5404B1EBE6AE8DE11" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D54F809-037E-4F89-9B3D-A32D9915A272}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAME1" sheetId="1" r:id="rId1"/>
@@ -26,28 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>1 1</t>
   </si>
@@ -65,6 +44,30 @@
   <si>
     <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>T T</t>
   </si>
 </sst>
 </file>
@@ -87,12 +90,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -107,8 +122,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -124,6 +144,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -393,29 +417,29 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>0</v>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -429,7 +453,7 @@
         <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -461,7 +485,7 @@
         <v>33</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -602,7 +626,7 @@
         <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -662,39 +686,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EBE11D4-C3F1-4754-8F8F-E27966025E14}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="2">
         <v>1</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="2">
         <v>11</v>
       </c>
-      <c r="C1">
-        <v>4</v>
-      </c>
-      <c r="D1">
+      <c r="C1" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3">
         <v>111</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="2">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1">
+      <c r="F1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2">
         <v>3</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="3">
         <v>3333</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J1" s="3">
+        <v>123123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>30</v>
       </c>
@@ -719,8 +746,11 @@
       <c r="I2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>45</v>
       </c>
@@ -745,8 +775,11 @@
       <c r="H3">
         <v>97</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -775,7 +808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>74</v>
       </c>
@@ -804,7 +837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C6">
         <v>17</v>
       </c>
@@ -818,7 +851,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>54</v>
       </c>
@@ -837,8 +870,11 @@
       <c r="I7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>21</v>
       </c>
@@ -861,7 +897,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>29</v>
       </c>
@@ -883,8 +919,11 @@
       <c r="I9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>24</v>
       </c>
@@ -901,7 +940,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>31</v>
       </c>
@@ -919,6 +958,9 @@
       </c>
       <c r="I11">
         <v>2</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
